--- a/bots/conversation_store.xlsx
+++ b/bots/conversation_store.xlsx
@@ -3,26 +3,38 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -33,7 +45,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -43,12 +62,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -131,10 +162,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -172,69 +203,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,54 +291,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -315,7 +347,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -324,7 +356,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -333,7 +365,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -341,10 +373,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -373,7 +405,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -386,13 +418,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -412,50 +443,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:E128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="67.36328125" customWidth="1" min="4" max="4"/>
-    <col width="49.90625" customWidth="1" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="67.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="49.86214285714286" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Session ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Conversation</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Summarization</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Generated Code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Analysed Data</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="409.5" customHeight="1">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="625.5" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>35307095-bf6d-45fd-a54e-13fad6f4278a</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -467,7 +501,8 @@
 assistant: Assistant: Perfect! I'll set a one-time reminder for you to wash the dishes tomorrow after lunch. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -500,14 +535,17 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>61123c4a-502f-4ee6-8e18-ab5ec34bc36c</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def handle_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -546,14 +584,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>f5d84e6f-575b-4f13-afc4-9092a4fe837e</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>user: hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -565,7 +604,7 @@
 assistant: Assistant: Perfect! I'll set a one-time reminder for you to wash the dishes tomorrow after lunch. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -590,7 +629,7 @@
 }</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -618,46 +657,53 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>da4bef50-5bd9-44e9-b9b7-a20fab92bca2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>90313a13-be8c-4e49-8817-33d35127b29a</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>8e6ca024-f25f-429a-931b-fbdc15dd5b02</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>user: no don't repeat
 assistant: Sure, I won't set the reminder to repeat. Could you please let me know what you need to be reminded about and when? For example, you could say "Remind me to water the plants at 7:00 PM today."</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -682,7 +728,7 @@
 }</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def handle_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -717,40 +763,47 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>e737ecc7-1e22-4798-a3a5-dc1db294c8fe</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>8cd82091-bd3c-4129-a46e-e7c315705db5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>fc985f60-c817-4d47-9d88-9f73a0cc417e</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -760,7 +813,7 @@
 assistant: Thank you for confirming! I'll set up a one-time reminder for you to clean the dishes tomorrow after dinner. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -785,7 +838,7 @@
 }</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -823,14 +876,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>7e920aaf-5ae6-4f97-bec8-861e27a6a501</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -840,7 +894,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes tomorrow after lunch, and it will be a one-time reminder. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -865,7 +919,7 @@
 }</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -893,27 +947,31 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>5ca639c2-6416-4be0-bab2-d557632ada48</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>user: just once
 assistant: What would you like to be reminded about?</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>8e37a2fe-f02d-49ad-ab16-eeb956898326</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -933,7 +991,7 @@
 assistant: Perfect! I'll set a one-time reminder for you to clean the dishes tomorrow after having dinner. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -958,7 +1016,7 @@
 }</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -995,14 +1053,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>23438cb3-8248-4442-b057-25e1212b052a</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1012,7 +1071,7 @@
 assistant: Perfect! I'll set up a one-time reminder for you to wash the dishes tomorrow after cooking. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1037,7 +1096,7 @@
 }</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1065,14 +1124,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>8bd97ef5-8127-43d6-9fb8-96c86571e5f3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>user: hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1084,7 +1144,7 @@
 assistant: Great! I'll set up a reminder for you to get food once you come home. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1109,7 +1169,7 @@
 }</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1139,14 +1199,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>6395480f-768c-48f4-b9b3-da54281d787e</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1158,7 +1219,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes after breakfast tomorrow. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1183,7 +1244,7 @@
 }</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1216,27 +1277,31 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>02a96979-fe99-4cb1-ae3f-58c25c537a30</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>user: just one time
 assistant: What would you like to be reminded about?</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>80db904c-4597-44f0-8e82-ac9ba3f0e817</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1246,7 +1311,7 @@
 assistant: Thank you for confirming! I'll set up a reminder for you to sing tomorrow after dinner, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1271,7 +1336,7 @@
 }</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1311,14 +1376,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>81be9910-8e6d-4504-b10d-4a85d94ab595</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1326,7 +1392,7 @@
 assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1351,7 +1417,7 @@
 }</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1388,14 +1454,15 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>4367301e-7817-47c7-b350-a238ad85d439</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>user: remind me to sing tomorrow after dinner jus once
 assistant: Great! Just to confirm, you would like a reminder to sing tomorrow after dinner, and you want this reminder to occur just once. Is that correct?
@@ -1403,7 +1470,7 @@
 assistant: Thank you for confirming! I'll set up a reminder for you to sing tomorrow after dinner, and it will occur just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1428,7 +1495,7 @@
 }</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1463,20 +1530,21 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>bc62fbdf-b5f2-4d5c-9c2d-0e3de561b85a</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>user: remind me to sing tomorrow after dinner just once
 assistant: Great! I'll set a reminder for you to sing tomorrow after dinner, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1501,7 +1569,7 @@
 }</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1541,14 +1609,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="409.5" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="1289.25" customFormat="1" customHeight="1" s="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>352889c0-ab1d-402a-99ea-62345a082f42</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1564,7 +1633,7 @@
 assistant: It seems we've already set up your reminder to wash your dishes tomorrow after having dinner, just for that day. If there's anything else you need help with, feel free to let me know! [ChatEnded]</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1589,7 +1658,7 @@
 }</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1624,27 +1693,31 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="E22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="32.25" customFormat="1" customHeight="1" s="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>4810827f-a764-4545-9a5c-a1465087face</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>user: can you remind me to wash my dishes tomorrow after having dinner
 assistant: Sure! Just to confirm, you would like a reminder to wash your dishes tomorrow after having dinner. Would you like this reminder to repeat, or is it just for tomorrow?</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="57.75" customFormat="1" customHeight="1" s="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>6096a75f-5480-4161-8a89-296265e79f11</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>user: just for tomorrow
 assistant: What would you like to be reminded about tomorrow?
@@ -1652,14 +1725,17 @@
 assistant: What specific task or event would you like to be reminded about tomorrow? For example, it could be something like "watering the plants" or "attending a meeting."</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>0df00b7c-83bd-41a8-bacc-6cb62f65d907</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1673,7 +1749,7 @@
 assistant: It seems like you've already set up a reminder for washing the dishes tomorrow after dinner. If there's anything else you need help with, feel free to let me know! [ChatEnded]</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1698,7 +1774,7 @@
 }</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1730,27 +1806,31 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="32.25" customFormat="1" customHeight="1" s="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>ca6e3ff5-c251-43fb-8ea5-293f85de10c2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="485.25" customFormat="1" customHeight="1" s="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>91aa7bcf-9f8a-4690-949e-785a0690a91f</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow morning after breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow morning after breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -1758,7 +1838,7 @@
 assistant: Perfect! I'll set a one-time reminder for you to wash the dishes tomorrow morning after breakfast. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1783,7 +1863,7 @@
 }</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1817,14 +1897,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="408" customFormat="1" customHeight="1" s="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>aeb06fa7-03da-441b-9047-58af96df8a7c</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1834,7 +1915,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes after having breakfast tomorrow, and it will be just for that day. If there's anything else you need, feel free to let me know. Otherwise, your reminder is all set! [ChatEnded]</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1859,7 +1940,7 @@
 }</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -1889,27 +1970,31 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="32.25" customFormat="1" customHeight="1" s="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>4bf68d36-8d63-418c-96a5-e94bb1f8bc58</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>2f26f689-a7cd-4472-975b-344b37b7f489</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -1921,7 +2006,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes after having breakfast tomorrow morning. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1946,14 +2031,16 @@
 }</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="459.75" customFormat="1" customHeight="1" s="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>870d987c-6cb5-4fd2-a8d4-944e83601a00</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after having breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after having breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -1961,7 +2048,7 @@
 assistant: Perfect! I'll set a one-time reminder for you to wash the dishes tomorrow after having breakfast. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -1986,7 +2073,7 @@
 }</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2020,14 +2107,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="E31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="433.5" customFormat="1" customHeight="1" s="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>d47071a1-583c-4459-a2fd-6e4bd87be58a</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes after breakfast tomorrow
 assistant: Great! I'll set a reminder for you to wash the dishes after breakfast tomorrow. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2035,7 +2123,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes after breakfast tomorrow. If you need any more reminders, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2060,7 +2148,7 @@
 }</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2092,14 +2180,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="446.25" customFormat="1" customHeight="1" s="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>91d29c7a-e6cc-4dee-8bda-4392ec1d71d7</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after having breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after having breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2107,7 +2196,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes tomorrow after having breakfast, just for tomorrow. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2132,7 +2221,7 @@
 }</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2166,14 +2255,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>712963fe-689f-45cf-9e10-844dbbbb75bd</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow morning after having breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow morning after having breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2181,7 +2271,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes tomorrow morning after having breakfast. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2206,7 +2296,7 @@
 }</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2236,14 +2326,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="433.5" customFormat="1" customHeight="1" s="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>7173997d-c2f1-4a18-a48b-4a0cadfc90ae</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after having dinner
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after having dinner. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2251,7 +2342,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes tomorrow after having dinner, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2276,7 +2367,7 @@
 }</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2308,14 +2399,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>7829ca50-f906-474f-a976-38a3a960c487</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after having breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after having breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2323,7 +2415,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes tomorrow after having breakfast, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2348,7 +2440,7 @@
 }</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2380,14 +2472,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>f5e86558-a2dc-4e02-af73-4f14f2f817a8</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after having breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after having breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2395,7 +2488,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes tomorrow after having breakfast, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2420,7 +2513,7 @@
 }</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2452,14 +2545,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>aaf09dad-5f21-499f-90ad-15f6234b8e7b</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2467,7 +2561,7 @@
 assistant: Perfect! I've set a reminder for you to wash the dishes tomorrow after breakfast, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2492,7 +2586,7 @@
 }</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2524,27 +2618,31 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="32.25" customFormat="1" customHeight="1" s="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>eb7563f3-673d-4cfd-965c-f35f416fb738</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after breakfast. Would you like this reminder to repeat, or is it just for tomorrow?</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="446.25" customFormat="1" customHeight="1" s="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>fa580559-38de-43c7-8c48-d18c67ab47d3</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after breakfast
 assistant: Great! Just to confirm, you would like a reminder to wash the dishes tomorrow after breakfast. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2552,7 +2650,7 @@
 assistant: Perfect! I'll set a reminder for you to wash the dishes tomorrow after breakfast, just for that day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2577,7 +2675,7 @@
 }</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2611,14 +2709,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="446.25" customFormat="1" customHeight="1" s="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>ce693a61-0395-4e17-b417-5a2593b9797a</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes after having breakfast
 assistant: Would you like this reminder to be set for today, tomorrow, or a specific date? Also, would you like it to repeat daily or just once?
@@ -2628,7 +2727,7 @@
 assistant: Perfect! I'll set a reminder for you to wash dishes after having breakfast tomorrow. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2653,7 +2752,7 @@
 }</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2687,14 +2786,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>21e4c47b-e0a0-43db-89ad-d83bc5a84e88</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>user: remind me to wash dishes tomorrow after dinner
 assistant: Great! I'll set a reminder for you to wash the dishes tomorrow after dinner. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -2702,7 +2802,7 @@
 assistant: Perfect! I'll set a one-time reminder for you to wash the dishes tomorrow after dinner. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2727,7 +2827,7 @@
 }</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2759,14 +2859,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>8e81bb75-335b-44ca-9c23-45afb54d14f7</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -2778,7 +2879,7 @@
 assistant: Great! I'll set up a one-time reminder for you to close the door when you leave the house. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2803,7 +2904,7 @@
 }</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2819,14 +2920,15 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>750c878c-7c72-4a17-82b5-200075532f52</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>user: remind me close the door when it is open
 assistant: When would you like to be reminded to close the door? For example, "when I leave the house" or "before going to bed."
@@ -2836,7 +2938,7 @@
 assistant: Great! I'll set a one-time reminder for you to close the door when you leave the house. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2861,7 +2963,7 @@
 }</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2877,14 +2979,15 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="472.5" customFormat="1" customHeight="1" s="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>0450adc2-8c33-401c-99b4-e740944bd197</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>user: Hello
 assistant: Hello! How can I assist you with setting up a reminder today?
@@ -2898,7 +3001,7 @@
 assistant: Thank you for providing all the details! I'll set a reminder for you to put out the trash tomorrow at 8:00 AM, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -2923,7 +3026,7 @@
 }</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -2957,27 +3060,31 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="32.25" customFormat="1" customHeight="1" s="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>e447b85b-da2b-4384-b82a-142f039d1b65</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>user: Hi
 assistant: Hello! How can I assist you with setting up a reminder today?</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="485.25" customFormat="1" customHeight="1" s="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>5b70aafd-ccad-4dd9-8ec1-93752471eb2d</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>user: remind me sing after dinner tomorrow just once
 assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
@@ -2985,7 +3092,7 @@
 assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3010,7 +3117,7 @@
 }</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3045,14 +3152,15 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="511.5" customFormat="1" customHeight="1" s="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>20e388e3-4818-486c-b0be-57e79ef110e3</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>user: remind me sing after dinner tomorrow just once
 assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder to occur just once. Is that correct?
@@ -3060,7 +3168,7 @@
 assistant: Perfect! I've set up a reminder for you to sing after dinner tomorrow, and it will occur just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3085,7 +3193,7 @@
 }</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3123,20 +3231,21 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="485.25" customFormat="1" customHeight="1" s="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>74010f8b-83fc-429f-9135-572043359a93</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>user:  remind me sing after dinner tomorrow just once
 assistant: Great! I'll set a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3161,7 +3270,7 @@
 }</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3197,20 +3306,21 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="485.25" customFormat="1" customHeight="1" s="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>5ee368a4-fe34-499b-92fc-0d835142922a</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>user: remind me sing after dinner tomorrow just once
 assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3235,7 +3345,7 @@
 }</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3269,14 +3379,15 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="342.75" customFormat="1" customHeight="1" s="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>037e184f-7114-49e3-b94e-bd2cb117ca72</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>user: remind me to go for a walk after having dinner tomorrow
 assistant: Great! Just to confirm, you would like a reminder to go for a walk after having dinner tomorrow. Would you like this reminder to repeat, or is it just for tomorrow?
@@ -3284,7 +3395,7 @@
 assistant: Perfect! I'll set a one-time reminder for you to go for a walk after having dinner tomorrow. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3309,7 +3420,7 @@
 }</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3335,14 +3446,15 @@
 ```</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="485.25" customFormat="1" customHeight="1" s="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>a23535ff-747b-4187-83fa-22526006653b</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>user: remind me sing after dinner tomorrow just everyday
 assistant: Great! Let's set up your reminder. 
@@ -3355,7 +3467,7 @@
 assistant: Perfect! Your reminder to sing after dinner will be set for tomorrow and will repeat every day. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>{
   "content": {
@@ -3380,7 +3492,7 @@
 }</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>```python
 def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
@@ -3413,8 +3525,3356 @@
 ```</t>
         </is>
       </c>
+      <c r="E52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>44fee484-41c1-49da-b61a-78785b70c89e</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you with setting up a reminder today?
+user: remind me to go for a walk tomorrow morning
+assistant: Great! Would you like this reminder to repeat every morning, or just once for tomorrow?
+user: just once
+assistant: Thank you for the details! I'll set up a reminder for you to go for a walk tomorrow morning, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Go for a walk",
+    "date": "tomorrow",
+    "time": {
+      "exact_time": {
+        "start_time": "06:00",
+        "end_time": "12:00"
+      },
+      "time_inferred": "morning"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    if activity_data and activity_data.get('activity') == 'Eating' and activity_data.get('activity_status') == 'end':
+        return True
+    else:
+        return False
+```</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>61f2ab6d-096d-4e23-9260-81b6c121272e</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me sing in next 5 minutes
+assistant: Sure! I'll remind you to sing in 5 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just once
+assistant: Great! I'll set a one-time reminder for you to sing in 5 minutes. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Sing",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    if activity_data and activity_data.get('activity') == 'Eating' and activity_data.get('activity_status') == 'end':
+        return True
+    else:
+        return False
+```</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="446.25" customFormat="1" customHeight="1" s="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>4b1869f9-2818-4581-b6df-54311048ad10</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to think at 10 pm
+assistant: Great! I'll set a reminder for you to think at 10 PM. Would you like this reminder to repeat daily, weekly, or just once?
+user: just once
+assistant: Perfect! I'll set a one-time reminder for you to think at 10 PM. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Think",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "22:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    # Check if the exact time is specified
+    if time:
+        # Extract the hour from the ISO 8601 time format
+        current_hour = int(time[11:13])
+        # Check if the current time matches the exact time specified (22:00)
+        if current_hour == 22:
+            return True
+        else:
+            return False
+    # Check activity data for 'Meal_Preparation' with 'start' status
+    if activity_data:
+        if activity_data.get('activity') == 'Meal_Preparation' and activity_data.get('activity_status') == 'start':
+            return True
+    # Check state data for relevant sensors
+    if state_data:
+        # Check if any motion is detected in the kitchen
+        if state_data.get('kitchen_motion_sensor') == 'motionDetected':
+            return True
+        # Check if the fridge door is opened
+        if state_data.get('fridge_entry_sensor') == 'entryDetected':
+            return True
+        # Check if the microwave door is opened
+        if state_data.get('microwave_door_entry_sensor') == 'entryDetected':
+            return True
+    # If none of the conditions are met, return False
+    return False
+```
+</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>a7c8905e-a538-4c93-8472-c67668140da3</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me sing at 10 pm
+assistant: Great! Just to confirm, you would like a reminder to sing at 10 PM. Would you like this reminder to repeat daily, weekly, or just once?
+user: just once
+assistant: Thank you for confirming. I'll set up a one-time reminder for you to sing at 10 PM. If there's anything else you need, feel free to let me know! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Sing",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "22:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>614be480-307d-46a7-9af9-85836e525c4e</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to sing at 10 past 5 minutes
+assistant: Just to clarify, would you like the reminder to be set for 5:10 PM today, or is there a specific date you have in mind? Also, would you like this reminder to repeat, or is it just a one-time reminder?
+user: nope I am 22:05 pm
+assistant: Got it! I'll set a reminder for you to sing at 10:05 PM today. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: nope
+assistant: Great! I'll set a one-time reminder for you to sing at 10:05 PM today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Sing",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "22:05",
+        "end_time": "22:05"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="420.75" customFormat="1" customHeight="1" s="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>0843c65c-a279-44e0-ae19-658219bafd37</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to think at 10:10 pm
+assistant: Great! Would you like this reminder to be set for today, or would you prefer a different date? Also, should this reminder repeat, or would you like it just once?
+user: just once
+assistant: Perfect! I'll set a reminder for you to think at 10:10 PM today, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Think",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "22:10",
+        "end_time": "22:10"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    # Reminder task: Clean the kitchen
+    # Time inferred: morning
+    # Recurrence: once
+    # Check if the current time is in the morning (06:00 to 12:00)
+    if time:
+        from datetime import datetime
+        current_time = datetime.fromisoformat(time)
+        if not (6 &lt;= current_time.hour &lt; 12):
+            return False
+    # Check if the activity is Meal_Preparation and it has started
+    if activity_data:
+        if activity_data.get('activity') != 'Meal_Preparation' or activity_data.get('activity_status') != 'start':
+            return False
+    # Check if any relevant sensor in the kitchen is triggered
+    if state_data:
+        kitchen_sensors = [
+            'microwave_smart_cable', 'kitchen_motion_sensor', 'fridge_entry_sensor', 'microwave_door_entry_sensor'
+        ]
+        if not any(state_data.get(sensor) for sensor in kitchen_sensors):
+            return False
+    # If all relevant conditions are met, trigger the reminder
+    return True
+```
+</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="446.25" customFormat="1" customHeight="1" s="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>edb32833-6e0c-4efa-a456-baab4b1d78f7</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to think at 10:20 pm
+assistant: Great! Would you like this reminder to be set for today, or would you prefer a different date? Also, should this reminder repeat, or would you like it just once?
+user: just once
+assistant: Would you like the reminder to be set for today, or would you prefer a different date?
+user: just today
+assistant: Thank you for the details! I'll set a reminder for you to "think" at 10:20 PM today, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Think",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "22:20",
+        "end_time": "22:20"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    # Reminder task: Clean the kitchen
+    # Time inferred: morning
+    # Relevant sensors: kitchen_motion_sensor, fridge_entry_sensor, microwave_door_entry_sensor
+    # Check if the current time is in the morning (06:00 to 12:00)
+    if time:
+        from datetime import datetime
+        current_time = datetime.fromisoformat(time)
+        if not (6 &lt;= current_time.hour &lt; 12):
+            return False
+    # Check activity data for Meal_Preparation start
+    if activity_data:
+        if activity_data.get('activity') == 'Meal_Preparation' and activity_data.get('activity_status') == 'start':
+            return True
+    # Check state data for relevant sensors
+    if state_data:
+        if state_data.get('kitchen_motion_sensor', {}).get('motionDetected', False):
+            return True
+        if state_data.get('fridge_entry_sensor', {}).get('doorStatus', '') == 'open':
+            return True
+        if state_data.get('microwave_door_entry_sensor', {}).get('doorStatus', '') == 'open':
+            return True
+    # If none of the conditions are met, return False
+    return False
+```
+</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="381.75" customFormat="1" customHeight="1" s="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>fb8f6f08-389d-4dbb-ba6e-068c09194bb9</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>user: just remind me to say Hi in next 10 minutes don't use any sensors or activity
+assistant: Great! I'll set a reminder for you to say "Hi" in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just once
+assistant: Perfect! I'll set a one-time reminder for you to say "Hi" in 10 minutes. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Say Hi",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>```python
+def should_trigger_reminder(time=None, activity_data=None, state_data=None, blackboard=None):
+    # Check if the activity is 'Meal_Preparation' and the status is 'start'
+    if activity_data:
+        if activity_data.get('activity') == 'Meal_Preparation' and activity_data.get('activity_status') == 'start':
+            return True
+    # Check if the time is in the morning (inferred time)
+    if time:
+        from datetime import datetime
+        current_time = datetime.fromisoformat(time)
+        if 5 &lt;= current_time.hour &lt; 12:  # Morning time range
+            return True
+    # Check if any relevant sensor in the kitchen is triggered
+    if state_data:
+        kitchen_sensors = [
+            'microwave_smart_cable', 'kitchen_motion_sensor', 'fridge_entry_sensor', 'microwave_door_entry_sensor'
+        ]
+        for sensor in kitchen_sensors:
+            if state_data.get(sensor):
+                return True
+    # If none of the conditions are met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>36ce23b2-19be-4061-9b97-74663880ca6a</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>user: can you remind me to wash dishes after dinner
+assistant: Sure! Would you like this reminder to be set for today, or would you prefer a specific date? Also, would you like it to repeat daily, or just once?
+user: just for now
+assistant: Great! I'll set a reminder for you to wash the dishes after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity data is provided
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Eating' and the status is 'end'
+        if activity == 'Eating' and activity_status == 'end':
+            # Delay for 10 minutes (600 seconds) after breakfast
+            await asyncio.sleep(600)
+            return True
+    # If conditions are not met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>59526282-3086-48ef-9d86-ede9b2133911</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>user: can you remind me to wash dishes after dinner
+assistant: Sure! Would you like this reminder to be set for today, or would you like it to repeat on certain days?
+user: just for today
+assistant: Great! I'll set a reminder for you to wash the dishes after dinner today. Would you like to be reminded once, or several times leading up to the event?
+user: just once
+assistant: Perfect! I'll set a reminder for you to wash the dishes once after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity data is provided
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Eating' and has ended
+        if activity == 'Eating' and activity_status == 'end':
+            # Delay for 10 minutes (600 seconds) after 'Eating' ends
+            await asyncio.sleep(600)
+            return True
+    # If conditions are not met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="303.75" customFormat="1" customHeight="1" s="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>830d574f-8d2b-4467-bcab-b9bb18eccf51</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>user: can you remind me to wash dishes after dinner
+assistant: Sure! Would you like this reminder to be set for today, or would you like it to repeat on certain days?
+user: just for now
+assistant: Great! I'll set a one-time reminder for you to wash the dishes after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity_data is provided and relevant
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Eating' and has ended
+        if activity == 'Eating' and activity_status == 'end':
+            # Delay for 10 minutes (600 seconds) after 'Eating' ends
+            await asyncio.sleep(600)
+            return True
+    # If conditions are not met, return False
+    return False
+```
+This function checks if the 'Eating' activity has ended and then waits for 10 minutes before returning `True`, as specified in the reminder request. If the conditions are not met, it returns `False`.</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>868fb91f-9a4b-4bd4-8db7-e0bf896fcc1b</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes after dinner
+assistant: Would you like this reminder to be set for today, or would you prefer a specific date? Also, would you like the reminder to repeat daily, or just once?
+user: just once
+assistant: Great! I'll set a reminder for you to wash dishes after dinner just once. Would you like this reminder for today, or do you have a specific date in mind?
+user: today only
+assistant: Perfect! I'll set a reminder for you to wash dishes after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity data is provided
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Eating' and has ended
+        if activity == 'Eating' and activity_status == 'end':
+            # Delay for 10 minutes (600 seconds) after 'Eating' ends
+            await asyncio.sleep(600)
+            return True
+    # If conditions are not met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>b4be639d-53d5-4005-9f66-7cd307c949c3</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes after dinner
+assistant: Would you like this reminder to be set for today, or would you prefer a specific date? Also, would you like this reminder to repeat daily, or just once?
+user: just once
+assistant: Great! I'll set a reminder for you to wash dishes after dinner just once. Would you like this reminder for today, or do you have a specific date in mind?
+user: just for tday
+assistant: Perfect! I'll set a reminder for you to wash dishes after dinner today, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity data is provided
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Eating' and the status is 'end' (after dinner)
+        if activity == 'Eating' and activity_status == 'end':
+            return True
+    # If no relevant conditions are met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n"/>
+    </row>
+    <row r="66" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>4a2e72b0-1c23-44bc-8947-b261eeccabfe</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes in next 10 minutes
+assistant: Great! I'll set a reminder for you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: nope, it's just one time
+assistant: Perfect! I'll set a one-time reminder for you to wash the dishes in 10 minutes. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>```python
+def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if activity data is provided
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # Check if the activity is 'Meal_Preparation' and has ended
+        if activity == 'Meal_Preparation' and activity_status == 'end':
+            return True
+    # If no relevant conditions are met, return False
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="433.5" customFormat="1" customHeight="1" s="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>17899fde-1fe0-4d5e-a919-3505b44041c1</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes in the next 10 minutes
+assistant: Great! I'll remind you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just one time
+assistant: Perfect! I'll set a one-time reminder for you to wash the dishes in 10 minutes. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes in the next 10 minutes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if the task requires a delay
+    delay_required = "Wash dishes in the next 10 minutes" in "Wash dishes in the next 10 minutes"
+    # If delay is required, wait for 10 minutes
+    if delay_required:
+        await asyncio.sleep(10 * 60)  # 10 minutes delay
+    # Check activity data for relevant activity
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # No specific activity is mentioned for washing dishes, so we ignore activity data
+    # Check state data for relevant sensor input
+    if state_data:
+        # No specific sensor is mentioned for washing dishes, so we ignore state data
+    # Since the task is to wash dishes in the next 10 minutes, we assume the reminder is triggered after the delay
+    return True
+# Example usage:
+# asyncio.run(handle_reminder())
+```</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="408" customFormat="1" customHeight="1" s="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>241a61d4-5f00-4993-a863-b54d185361de</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes in the next 10 minutes
+assistant: Great! I'll remind you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just one time
+assistant: Perfect! I'll set a one-time reminder for you to wash the dishes in 10 minutes. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes in the next 10 minutes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if the task requires a delay
+    delay_required = "Wash dishes in the next 10 minutes" in "Wash dishes in the next 10 minutes"
+    # If delay is required, use asyncio to handle it
+    if delay_required:
+        await asyncio.sleep(600)  # 10 minutes delay
+    # Check activity data for relevant activity
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # No specific activity is mentioned in the task, so we ignore activity data
+    # Check state data for relevant sensor input
+    if state_data:
+        # No specific sensor is mentioned in the task, so we ignore state data
+    # Since the task is to wash dishes in the next 10 minutes, we assume the reminder should be triggered after the delay
+    return True
+# Example usage:
+# asyncio.run(handle_reminder())
+```</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n"/>
+    </row>
+    <row r="69" ht="459.75" customFormat="1" customHeight="1" s="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>142c293c-e484-4f46-93b4-e9a003a7bf49</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes in next 10 minutes
+assistant: Sure! I'll set a reminder for you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just for this one time?
+user: just one time
+assistant: Great! I'll set a one-time reminder for you to wash the dishes in 10 minutes. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes in next 10 minutes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    # Check if the task requires a delay
+    delay_required = True  # "in next 10 minutes" implies a delay
+    # Check activity data for relevant activity
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        # No specific activity is mentioned in the task, so we ignore activity data
+    # Check state data for relevant sensor input
+    if state_data:
+        # No specific sensor input is mentioned in the task, so we ignore state data
+    # Handle delay using asyncio if required
+    if delay_required:
+        await asyncio.sleep(600)  # 10 minutes delay
+    # Since no specific activity or sensor condition is mentioned, we assume the reminder is triggered after the delay
+    return True
+# Example usage:
+# asyncio.run(handle_reminder())
+```
+This function is designed to handle the reminder request "Wash dishes in next 10 minutes" by introducing a 10-minute delay using `asyncio.sleep`. Since no specific activity or sensor condition is mentioned in the task, the function assumes the reminder is triggered after the delay.</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>62bb5387-6311-4d81-999c-d6fc959314db</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes next 10 minutes
+assistant: Great! I'll set a reminder for you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just once
+assistant: Perfect! I'll set a one-time reminder for you to wash the dishes in 10 minutes. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes in 10 minutes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        if activity == 'Meal_Preparation' and activity_status == 'end':
+            await asyncio.sleep(600)  # 10 minutes delay
+            return True
+    return False
+```</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
+    </row>
+    <row r="71" ht="278.25" customFormat="1" customHeight="1" s="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>f77e715d-1d3f-40e6-af40-6be0a6623c68</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>user: remind me to wash dishes in next 10 minutes
+assistant: Sure! I'll set a reminder for you to wash the dishes in 10 minutes. Would you like this reminder to repeat, or is it just a one-time reminder?
+user: just once
+assistant: Great! I'll set a one-time reminder for you to wash the dishes in 10 minutes. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash dishes in next 10 minutes",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>```python
+import asyncio
+async def handle_reminder(activity_data=None, state_data=None, blackboard=None):
+    task = "Wash dishes in next 10 minutes"
+    if "10 minutes" in task:
+        await asyncio.sleep(10 * 60)
+        return True
+    else:
+        return True
+# Example usage:
+# asyncio.run(handle_reminder())
+```</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9e2e30e6-0e6b-4834-a400-a0450b81c40b</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?
+user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be for today, or would you prefer a specific date? Also, should it repeat, or would you like it just once?
+user: just for today
+assistant: Perfect! I'll set up a reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>258eaec6-8fd8-47a7-b5d7-b81162c925ef</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be a one-time event, or would you like it to repeat on certain days?
+user: just for today
+assistant: Perfect! I'll set up a one-time reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ed3c989a-e644-4799-9d7f-ce47ffac5bb5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be a one-time event, or would you like it to repeat on certain days?
+user: just for today
+assistant: Perfect! I'll set up a one-time reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>844ad7a5-0e34-44f1-91e2-908b6fa10f64</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be a one-time event, or should it repeat on certain days?
+user: just for today
+assistant: Perfect! I'll set up a one-time reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fbecd600-3b6f-4b9f-876f-b6ba5d26aa76</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be for today, or would you prefer a specific date? Also, would you like it to repeat, or just once?
+user: just for today
+assistant: Perfect! I'll set up a reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>542b3586-bbd0-4082-af09-6689d0e8e728</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be a one-time event, or should it repeat on certain days?
+user: for today
+assistant: Perfect! I'll set up a one-time reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>from datetime import datetime, timedelta
+def reminder_d358c511_1db3_42ff_bfd6_0f272db82caa(current_time, activity_data=None, state_data=None, blackboard=None):
+    # Extract task and delay information
+    task_description = "Do laundry"
+    delay_minutes = 0
+    if "after breakfast" in task_description:
+        delay_minutes = 10  # Example delay for "after breakfast"
+    # Calculate target time if delay is specified
+    if delay_minutes &gt; 0:
+        target_time = current_time + timedelta(minutes=delay_minutes)
+    else:
+        target_time = current_time
+    # Check activity data
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        if activity == 'Eating' and activity_status == 'end':
+            if current_time &gt;= target_time:
+                return True
+            else:
+                return False
+    # Check state data (not used in this example)
+    if state_data:
+        pass
+    # Check blackboard (not used in this example)
+    if blackboard:
+        pass
+    # If no activity or state data is relevant, rely on delay
+    if delay_minutes &gt; 0 and current_time &gt;= target_time:
+        return True
+    return False</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>b3e9b6b0-4c54-425e-b764-fed4501caf35</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be a one-time event, or would you like it to repeat on certain days?
+user: just for today
+assistant: Perfect! I'll set up a one-time reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>from datetime import datetime, timedelta
+def reminder_aae533de_f195_47e9_a8cd_48eb84458f97(current_time, activity_data=None, state_data=None, blackboard=None):
+    # Extract task and delay information
+    task_description = "Do laundry"
+    delay_minutes = 0
+    if "after breakfast" in task_description:
+        delay_minutes = 10  # Example delay for "after breakfast"
+    # Calculate target time if delay is specified
+    if delay_minutes &gt; 0:
+        target_time = current_time + timedelta(minutes=delay_minutes)
+    else:
+        target_time = current_time
+    # Check activity data
+    if activity_data:
+        activity = activity_data.get('activity')
+        activity_status = activity_data.get('activity_status')
+        if activity == 'Eating' and activity_status == 'end':
+            if current_time &gt;= target_time:
+                return True
+            else:
+                return False
+    # Check state data (not used in this example)
+    if state_data:
+        pass
+    # Check blackboard (not used in this example)
+    if blackboard:
+        pass
+    # If no activity or state data is relevant, rely on delay
+    if delay_minutes &gt; 0 and current_time &gt;= target_time:
+        return True
+    return False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>c71c0f47-4921-4a16-a64d-cb7aa6bc9506</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>user: emind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be for today, or would you like to specify a different date? Also, would you like this reminder to repeat, or just happen once?
+user: just for today
+assistant: Perfect! I'll set up a reminder for you to sing after dinner today. It will be a one-time reminder. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>70fe0f37-71cd-4009-94c4-19ed5f5298f8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to be for today, or would you like to specify a different date? Also, would you like this reminder to repeat, or just happen once?
+user: just for today
+assistant: Perfect! I'll set up a reminder for you to sing after dinner today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>def reminder_375bcc77_2e52_4359_bb14_aa49ff5be89f(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>e8f45daa-4610-4100-83ae-56a551913ef3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner
+assistant: Great! I'll set up a reminder for you to sing after dinner. Would you like this reminder to repeat every day, or just once?
+user: just for day
+assistant: Thank you for clarifying! I'll set up a reminder for you to sing after dinner just for today. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>def reminder_9149761f_8933_442c_a3fc_758ee4e103c0(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4faf199e-4a63-4a64-acb9-2dda4f0cb491</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>def reminder_e1adf3b3_fed7_4942_a8c8_63372633381b(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>d545a77e-2362-451d-bf21-4c66b6013a71</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>user:  remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: just for today
+assistant: Got it! I'll set a reminder for you to sing after dinner today, and it will be just once. Is there anything else you need help with?
+user: yes just once
+assistant: Perfect! I've set a reminder for you to sing after dinner today, and it will be just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>def reminder_bbe7fda6_73a3_4e2d_805b_e81a79f40cbf(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>6651cc78-a250-4a8a-bcc8-b5f234b129b6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: just for today
+assistant: Thank you for clarifying! So, you would like a reminder to sing after dinner today, and you want this reminder just once. Is that correct?
+user: just once
+assistant: Thank you for confirming! I will set a reminder for you to sing after dinner today, and it will be just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>def reminder_9ea67a62_d41c_4cf7_b22c_630554c4136c(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>68708679-00e6-4b4c-aeb4-9b468127d436</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "09:00",
+        "end_time": "10:00"
+      },
+      "time_inferred": "after breakfast"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>def reminder_24c2e681_abda_4d7d_90f3_b67c3dc97df7(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4267fa74-ed61-4e03-8b01-048f4ddc9ecc</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>def reminder_6c8a4125_5f3d_4e41_ac82_6cab9e1c7eff(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>855d4841-83b0-4467-97d5-b9ec8b509580</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>def reminder_effe67d4_5ee9_41a6_ac81_c59d2dddda32(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fd23f60e-c2f8-43a8-b7d2-706e7215fce1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>def reminder_c0a0976a_e60e_48df_b011_da7ab8145727(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>529424a6-a5ee-4d73-bdd7-38ede35f5be5</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>def reminder_7c6e71ff_059b_439a_a3e4_0b58c56ff959(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1d9c8185-6bb6-4fdb-a16a-e48c79b5c4f5</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>user:  remind me sing after dinner tomorrow just once
+assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>def reminder_89fbef6a_1d94_4602_9833_f66e9d160694(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>713e6723-d6e4-4a90-8f38-459cf107ca0b</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>def reminder_972e2917_0a05_4a80_b9fe_66dbb64d1f6c(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activtity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fc27e513-55c3-4049-b993-07b2afdd6133</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>def reminder_a3f7d4e0_ce5a_45c0_a0ef_7162be3d3bb6(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>b9a003c2-bf03-4fbb-890d-0a05161cd9c1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>def reminder_77b192bf_d97f_47af_b76a_5fdc8358e93e(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2a9a0be0-0e43-4ad8-8f32-2a512bfcefeb</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>def reminder_1464cceb_25ad_4873_a667_bb66a4b6cfd7(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1622e851-0887-4f9b-bea0-f43c8b4412c9</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! I'll set up a reminder for you to sing after dinner tomorrow, and it will be just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>def reminder_655e8851_8106_4db1_a6f1_fe11554396a7(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>6773c5be-7ca6-4367-afcf-776dce80e59d</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>def reminder_e1b09659_79dc_4b63_9ea9_70eff414c1c0(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>385a2473-a48e-4a57-a18d-402579c111e6</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>def reminder_cc50a526_7ef7_40f8_bea3_306cfefb5f4c(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>154cc36b-769d-4eca-a727-d63399914f25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "21:00",
+        "end_time": "23:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>def reminder_eafa7d9d_4c80_4602_9611_77f448a086df(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>95e6872f-9780-4f5a-a659-20ab82a62b6d</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "20:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>def reminder_4ad42283_eb39_46bf_b676_505febb3839d(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1d6d56b7-1ffc-4578-8cf4-e10e0d5d9c20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "20:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>def reminder_29fe3ee3_68d9_4381_b7fb_9758fafe2b8c(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7e4065d4-e298-4b43-85a0-7aa21829a1a3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "20:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>def reminder_b22cb0da_ce63_4e2b_88e1_5023d7703f46(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4c8e3954-6ffa-4b1d-8162-8eb64b086908</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]
+user: yes
+assistant: It looks like you've already set a reminder to sing after dinner tomorrow, just once. If there's anything else you need help with, feel free to let me know!</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "20:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>def reminder_467119de_5a31_463b_aa93_b5a892eb0a26(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4aa2b33d-6133-403e-b5b7-a11518d46427</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "20:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>def reminder_62872cbf_c7b9_4757_aca0_34483dde458d(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>b0f45922-e0e4-455f-a6a4-e52506a30f6c</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>def reminder_4b3a8db8_6426_4082_9660_a31771b258d9(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('activity_status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>886134a3-4d95-4262-93b4-ac7fa4c30281</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set a reminder for you to sing after dinner tomorrow, just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>def reminder_4f827f24_8a69_4cc1_a03d_17e4d2b47876(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>d5bd426e-9259-419d-9fcc-c1db6eee2f0c</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>user:  remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>def reminder_26dd4cac_7ac2_40ce_ac83_6ed9fb64a4f2(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>8138dedd-c537-40d8-8798-c8649c828101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>user:  remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>def reminder_1ae876aa_4aab_4e5e_9a78_cd25f8879e66(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>abed08b7-e687-428f-bf3d-062a9b400684</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>user: remind me to sing after dinner just for today
+assistant: Great! I'll set up a reminder for you to sing after dinner just for today. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "18:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>def reminder_68be6250_da23_4dc8_b578_2b43834ea996(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>e55bc9bf-b89c-4394-8cd4-5986bcab49f2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Perfect! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "13:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>def reminder_bff03942_1640_4739_bcb2_368761758fbe(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>e603d3a8-5bb2-4fda-b299-0589401a7ae7</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>user: remind me to Wash hands after eating
+assistant: Great! When would you like to be reminded to wash your hands after eating? Would you like this reminder to be set for a specific time, or perhaps after every meal?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>8b5aaae0-3a11-4fe8-ba9e-fe6e83c820d0</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>user: no just once
+assistant: It seems like you want a one-time reminder. Could you please let me know what you need to be reminded about and when you would like the reminder? For example, you could say, "Remind me to water the plants at 7:00 PM" or "Remind me to take out the trash when I come home."</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4d52569c-2508-44bf-92b5-70dfa95666f8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you today? If you need help setting up a reminder, just let me know what you need to be reminded about.
+user: remind me to sing after dinner
+assistant: Great! I can help with that. When would you like to be reminded to sing after dinner? You could specify a time, or I can set it for a certain event, like "when I finish eating." Let me know what works best for you!
+user: when I finish eating
+assistant: Currently, I'm unable to set a reminder specifically for "when you finish eating," but I'm always improving and may support it in the future. Would you like to set a time-based reminder instead? For example, I could remind you at a specific time after dinner. Let me know what works for you!</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>d8fb6246-c694-4c73-bc4e-6513c4fce238</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>user: hello
+assistant: Hello! How can I assist you today? If you need help setting up a reminder, just let me know what you need to be reminded about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>b1ca8488-6499-428a-9a1a-0e3f1ff3e2b9</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you with setting up a reminder today?</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3fd9861f-c575-4ec7-9f24-f1aab046cb92</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you with setting up a reminder today?</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9bfffb4b-8ccf-4fc7-9471-39fc73f03f46</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you with setting up a reminder today? Is there something specific you need to be reminded about, like a household task or a personal event?</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>824da0dd-13d1-42bd-85e2-cdd6d5234259</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>5c41de26-8d69-4168-8a6e-5d33b6676c98</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1e9f44c2-76fa-4200-90b3-d1d984cfe61e</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! How can I assist you with setting up a reminder today? Is there something specific you need to be reminded about?</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ea961c07-8502-42f0-910b-506f81fe7cb4</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?
+user: remind me sing after dinner tomorrow just once
+assistant: Great! You'd like a reminder to sing after dinner tomorrow. Let's set that up. 
+Since we don't have a specific sensor for detecting when dinner ends, would you like to set a specific time for this reminder instead? For example, "Remind me at 8:00 PM tomorrow." 
+Let me know what works best for you!</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ae1eec13-ead0-4dce-8a01-5cd08af70c18</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?
+user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, which is January 3, 2025, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! I'll set up a reminder for you to sing after dinner on January 3, 2025, and it will be just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>c40e5c87-534b-44af-950b-fbe2ae1c3e42</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Let's set up your reminder. Here's what I have:
+- **Task**: Sing
+- **Time/Event**: After dinner
+- **Date**: Tomorrow (2025-01-03)
+- **Recurrence**: Just once
+Does everything look correct? If so, I'll go ahead and set the reminder for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>45e42d49-993e-4fb1-b4a7-f4481e7a09a6</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Let's set up your reminder. Here's what I have:
+- **Task**: Sing
+- **Time/Event**: After dinner
+- **Date**: Tomorrow
+- **Recurrence**: Just once
+Does everything look correct? If so, I'll go ahead and set the reminder for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>00d00b89-113b-4d4b-bb1f-9241b2f7e1a5</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Thank you for confirming! I'll set up a reminder for you to sing after dinner tomorrow, and it will be just once. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "13:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>from datetime import datetime, timedelta
+def reminder_b8781ab2_279d_4482_bfe5_22e8672d3d1f(current_time, activity_data=None, state_data=None, blackboard=None):
+    task_description = "Do laundry"
+    delay_minutes = None
+    activity_trigger = None
+    state_trigger = None
+    if "after Dinner" in task_description:
+        activity_trigger = ('Eating', 'end')
+    if "10 minutes" in task_description:
+        delay_minutes = 10
+    if activity_trigger:
+        if activity_data and activity_data.get('activity') == activity_trigger[0] and activity_data.get('activity_status') == activity_trigger[1]:
+            if delay_minutes is not None:
+                target_time = current_time + timedelta(minutes=delay_minutes)
+                if datetime.now() &gt;= target_time:
+                    return True
+            else:
+                return True
+    if delay_minutes is not None and not activity_trigger:
+        target_time = current_time + timedelta(minutes=delay_minutes)
+        if datetime.now() &gt;= target_time:
+            return True
+    return False</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2697eaa0-f827-4bfc-a3ff-79af7528cbae</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>user: remind me sing after dinner tomorrow just once
+assistant: Great! Let's set up your reminder. 
+- **Task**: Sing
+- **Time/Event**: After dinner
+- **Date**: Tomorrow
+- **Recurrence**: Just once
+Does everything look correct? If so, I'll go ahead and set the reminder for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>5d58716e-4b88-4359-a530-a13b381ff9ec</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?
+user: yes
+assistant: It sounds like you're ready to set up a reminder! Could you please let me know what you need to be reminded about? For example, it could be a household task or a personal event.
+user: remind me sing after dinner tomorrow just once
+assistant: Great! I'll set up a reminder for you to sing after dinner tomorrow, just once. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Do laundry",
+    "date": null,
+    "time": {
+      "exact_time": {
+        "start_time": "13:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": "after Dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>def reminder_1ec23c14_3d11_434c_a2e2_63b73918226e(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return time and blackboard.get('medicine_time') and time &gt;= blackboard['medicine_time']</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>adedcf9c-5273-45fb-ba2e-7b3be88f2e41</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>user: Hello
+assistant: Hello! I'm here to help you set up a reminder. What would you like to be reminded about?
+user: remind me sing after dinner tomorrow just once
+assistant: Great! Just to confirm, you would like a reminder to sing after dinner tomorrow, and you want this reminder just once. Is that correct?
+user: yes
+assistant: Great! Your reminder to sing after dinner tomorrow has been set, and it will remind you just once. If there's anything else you need, feel free to let me know. Have a wonderful day! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Sing",
+    "date": "tomorrow",
+    "time": {
+      "exact_time": {
+        "start_time": "19:00",
+        "end_time": "21:00"
+      },
+      "time_inferred": "after dinner"
+    },
+    "recurrence": {
+      "type": "once",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>def reminder_c5a5ca31_5a1f_4349_a272_ad3504c7ee01(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return time and datetime.fromisoformat(time) &gt;= datetime.now() + timedelta(minutes=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>65905ab5-d7cb-4271-b300-46cbe826e754</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>user: remind me wash hands after lunch
+assistant: Great! I'll set up a reminder for you to wash your hands after lunch. Would you like this reminder to be for today, or would you like it to repeat daily?
+user: yes repeat it daily
+assistant: Great! I'll set up a daily reminder for you to wash your hands after lunch. Is there anything else you need help with? If not, your reminder is all set! [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Wash hands",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "13:00",
+        "end_time": "14:00"
+      },
+      "time_inferred": "after lunch"
+    },
+    "recurrence": {
+      "type": "daily",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>def reminder_b01e7cd3_ac3e_419c_8da3_6ebb7dafe248(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/bots/conversation_store.xlsx
+++ b/bots/conversation_store.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -6874,6 +6874,72 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>0122f583-7231-45ba-8f84-075e5f4a460a</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>user: Are you working?
+assistant: Hello! I'm here to help you set up reminders. What would you like to be reminded about?
+user: Remind me to take out the trash after lunch
+assistant: Great! I'll set up a reminder for you to take out the trash after lunch. 
+Would you like this reminder to be for today, tomorrow, or a specific date? Also, should it repeat daily, weekly, or just once?
+user: Repeat it daily
+assistant: Perfect! I'll set up a daily reminder for you to take out the trash after lunch. Is there a specific time you'd like me to set for "after lunch," or should I leave it open-ended?</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3589071e-dd20-4fae-a014-6aaad301d227</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>user: please remind me to take out the trash after lunch
+assistant: Great! I'll set up a reminder for you to take out the trash after lunch. Would you like this reminder to be for today, or would you like it to repeat on certain days?
+user: every day
+assistant: Thank you for the information! I'll set up a daily reminder for you to take out the trash after lunch. If there's anything else you need, feel free to let me know. [ChatEnded]
+user: every day
+assistant: It looks like you've already set up a daily reminder to take out the trash after lunch. If there's anything else you need help with, feel free to let me know!</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Take out the trash",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "13:00",
+        "end_time": "14:00"
+      },
+      "time_inferred": "after lunch"
+    },
+    "recurrence": {
+      "type": "daily",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>def reminder_c384b472_0776_4be8_8301_7c9b7af929ca(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Eating" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bots/conversation_store.xlsx
+++ b/bots/conversation_store.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -6940,6 +6940,57 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>046296d5-5131-43e6-9fe2-b39cce47c2c6</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>user: Please set a reminder for 10PM that I need a reminder for 10PM
+assistant: It looks like you want a reminder set for 10 PM. Could you please let me know what you need to be reminded about at that time?
+user: Remind me to set a reminder
+assistant: Could you please clarify what you would like to be reminded about at 10 PM? For example, it could be a task like "watering the plants" or "taking out the trash." Let me know so I can set up the reminder for you!
+user: I'm not sure what to be reminded about yet. Why can't I just have a general reminder reminder?
+assistant: I understand you're looking for a general reminder at 10 PM. While I specialize in setting reminders for specific tasks or events, I can certainly set a reminder for you to think about what you might need to be reminded of at that time. Would you like this reminder to repeat daily, or just once for today?
+user: Every day please.
+assistant: Great! I'll set up a daily reminder for you at 10 PM to think about what you might need to be reminded of. If you ever decide on a specific task or event, feel free to let me know, and I can update the reminder for you. 
+[ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Think about what you might need to be reminded of",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": "22:00",
+        "end_time": "22:00"
+      },
+      "time_inferred": null
+    },
+    "recurrence": {
+      "type": "daily",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>def reminder_6ea0930c_41e5_4785_9735_9c5f282d6304(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return time and datetime.fromisoformat(time) &gt;= datetime.now() + timedelta(minutes=10)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bots/conversation_store.xlsx
+++ b/bots/conversation_store.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -6991,6 +6991,113 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0c3327d3-7342-47f3-b3c5-a6b276e87233</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>user: remind me to eat after I wake up
+assistant: Great! I'll set up a reminder for you to eat after you wake up. Would you like this reminder to repeat every day, or just once?
+user: every day
+assistant: Thank you for the information! I'll set up a daily reminder for you to eat after you wake up. If there's anything else you need, feel free to let me know. [ChatEnded]</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Eat after I wake up",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": "after I wake up"
+    },
+    "recurrence": {
+      "type": "daily",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>def reminder_ad765cf2_8340_47a9_9902_216a1abd5384(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return activity_data.get('activity') == "Sleeping" and activity_data.get('status') == "end"</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>677bea34-81dc-49a7-af24-2ca3f093b7f1</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>user: I want to go eat banana after dinner
+assistant: Great! I can help you set a reminder for that. 
+1. **Time/Event**: When would you like to be reminded? For example, "Remind me right after dinner" or "Remind me at 8:00 PM."
+2. **Date (Optional)**: Would you like this reminder for today, tomorrow, or a specific date?
+3. **Recurrence**: Should this reminder repeat, or is it just for one time?
+Let me know these details, and I'll set up the reminder for you!</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>789c9091-8112-449c-9586-59fe1d5ef8e9</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>user: Please remind me to watch tv after dinner
+assistant: Great! I'll set up a reminder for you to watch TV after dinner. Would you like this reminder for today, or would you prefer a specific date? Also, should this reminder repeat, or would you like it just once?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>{
+  "content": {
+    "task": "Bring in my cactus",
+    "date": "today",
+    "time": {
+      "exact_time": {
+        "start_time": null,
+        "end_time": null
+      },
+      "time_inferred": "when it starts raining"
+    },
+    "recurrence": {
+      "type": "daily",
+      "details": {
+        "days": null,
+        "occurrence_frequency": "once"
+      }
+    },
+    "priority": "medium"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>def reminder_55146fe5_00eb_4e89_a608_45ad3722e967(time=None, activity_data=None, sensor_data=None, blackboard=None):
+    return sensor_data.get('rain_sensor', {}).get('status', False)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
